--- a/Data-Aset-Transmisi.xlsx
+++ b/Data-Aset-Transmisi.xlsx
@@ -6,13 +6,15 @@
     <sheet state="visible" name="SKTT" sheetId="1" r:id="rId5"/>
     <sheet state="visible" name="TOWER" sheetId="2" r:id="rId6"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">SKTT!$A$1:$Y$337</definedName>
+  </definedNames>
   <calcPr/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2592" uniqueCount="751">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1696" uniqueCount="751">
   <si>
     <t>UPT</t>
   </si>
@@ -2340,7 +2342,7 @@
     <xf borderId="2" fillId="0" fontId="2" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="2" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -2626,16 +2628,16 @@
         <v>7</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D3" s="3">
-        <v>-6.243098824E9</v>
+        <v>-6.243098712E9</v>
       </c>
       <c r="E3" s="3">
-        <v>1.066405675E9</v>
+        <v>1.066406036E9</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4">
@@ -2646,13 +2648,13 @@
         <v>7</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D4" s="3">
-        <v>-6.243098824E9</v>
+        <v>-6.241099771E9</v>
       </c>
       <c r="E4" s="3">
-        <v>1.066405675E9</v>
+        <v>1.066378684E9</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>9</v>
@@ -2666,16 +2668,16 @@
         <v>7</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D5" s="3">
-        <v>-6.243098712E9</v>
+        <v>-6.239057561E9</v>
       </c>
       <c r="E5" s="3">
-        <v>1.066406036E9</v>
+        <v>1.066345006E9</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6">
@@ -2686,16 +2688,16 @@
         <v>7</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D6" s="3">
-        <v>-6.241099771E9</v>
+        <v>-6.241009205E9</v>
       </c>
       <c r="E6" s="3">
-        <v>1.066378684E9</v>
+        <v>1.066379133E9</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7">
@@ -2706,13 +2708,13 @@
         <v>7</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D7" s="3">
-        <v>-6.241099771E9</v>
+        <v>-6.237648805E9</v>
       </c>
       <c r="E7" s="3">
-        <v>1.066378684E9</v>
+        <v>1.06630972E8</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>9</v>
@@ -2726,13 +2728,13 @@
         <v>7</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D8" s="3">
-        <v>-6.241099771E9</v>
+        <v>-6.233593294E9</v>
       </c>
       <c r="E8" s="3">
-        <v>1.066378684E9</v>
+        <v>1.066323963E9</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>9</v>
@@ -2746,16 +2748,16 @@
         <v>7</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D9" s="3">
-        <v>-6.239057561E9</v>
+        <v>-6.23893105E8</v>
       </c>
       <c r="E9" s="3">
-        <v>1.066345006E9</v>
+        <v>1.066344731E9</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10">
@@ -2766,13 +2768,13 @@
         <v>7</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D10" s="3">
-        <v>-6.239057561E9</v>
+        <v>-6.229564549E9</v>
       </c>
       <c r="E10" s="3">
-        <v>1.066345006E9</v>
+        <v>1.06633938E8</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>9</v>
@@ -2786,16 +2788,16 @@
         <v>7</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="D11" s="3">
-        <v>-6.241009205E9</v>
+        <v>-6.229744972E9</v>
       </c>
       <c r="E11" s="3">
-        <v>1.066379133E9</v>
+        <v>1.066369928E9</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12">
@@ -2806,16 +2808,16 @@
         <v>7</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="D12" s="3">
-        <v>-6.237648805E9</v>
+        <v>-6.237594186E9</v>
       </c>
       <c r="E12" s="3">
-        <v>1.06630972E8</v>
+        <v>1.066310893E9</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13">
@@ -2826,13 +2828,13 @@
         <v>7</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="D13" s="3">
-        <v>-6.237648805E9</v>
+        <v>-6.230659037E9</v>
       </c>
       <c r="E13" s="3">
-        <v>1.06630972E8</v>
+        <v>1.066399788E9</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>9</v>
@@ -2846,13 +2848,13 @@
         <v>7</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="D14" s="3">
-        <v>-6.239057561E9</v>
+        <v>-6.227639166E9</v>
       </c>
       <c r="E14" s="3">
-        <v>1.066345006E9</v>
+        <v>1.066395435E9</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>9</v>
@@ -2866,16 +2868,16 @@
         <v>7</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="D15" s="3">
-        <v>-6.233593294E9</v>
+        <v>-6.233502337E9</v>
       </c>
       <c r="E15" s="3">
-        <v>1.066323963E9</v>
+        <v>1.066325677E9</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="16">
@@ -2886,13 +2888,13 @@
         <v>7</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="D16" s="3">
-        <v>-6.233593294E9</v>
+        <v>-6.225292264E9</v>
       </c>
       <c r="E16" s="3">
-        <v>1.066323963E9</v>
+        <v>1.066381989E9</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>9</v>
@@ -2906,16 +2908,16 @@
         <v>7</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="D17" s="3">
-        <v>-6.23893105E8</v>
+        <v>-6.223488847E9</v>
       </c>
       <c r="E17" s="3">
-        <v>1.066344731E9</v>
+        <v>1.06642377E8</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18">
@@ -2926,16 +2928,16 @@
         <v>7</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="D18" s="3">
-        <v>-6.229564549E9</v>
+        <v>-6.229491928E9</v>
       </c>
       <c r="E18" s="3">
-        <v>1.06633938E8</v>
+        <v>1.066340282E9</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="19">
@@ -2946,13 +2948,13 @@
         <v>7</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="D19" s="3">
-        <v>-6.229564549E9</v>
+        <v>-6.221957552E9</v>
       </c>
       <c r="E19" s="3">
-        <v>1.06633938E8</v>
+        <v>1.066462758E9</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>9</v>
@@ -2966,13 +2968,13 @@
         <v>7</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="D20" s="3">
-        <v>-6.237648805E9</v>
+        <v>-6.220661734E9</v>
       </c>
       <c r="E20" s="3">
-        <v>1.06630972E8</v>
+        <v>1.066500488E9</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>9</v>
@@ -2986,16 +2988,16 @@
         <v>7</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="D21" s="3">
-        <v>-6.229744972E9</v>
+        <v>-6.229754043E9</v>
       </c>
       <c r="E21" s="3">
-        <v>1.066369928E9</v>
+        <v>1.066369838E9</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="22">
@@ -3006,13 +3008,13 @@
         <v>7</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="D22" s="3">
-        <v>-6.229744972E9</v>
+        <v>-6.22006072E8</v>
       </c>
       <c r="E22" s="3">
-        <v>1.066369928E9</v>
+        <v>1.066542847E9</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>9</v>
@@ -3026,13 +3028,13 @@
         <v>7</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="D23" s="3">
-        <v>-6.237594186E9</v>
+        <v>-6.230677813E9</v>
       </c>
       <c r="E23" s="3">
-        <v>1.066310893E9</v>
+        <v>1.066399892E9</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>11</v>
@@ -3046,16 +3048,16 @@
         <v>7</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="D24" s="3">
-        <v>-6.230659037E9</v>
+        <v>-6.227648237E9</v>
       </c>
       <c r="E24" s="3">
-        <v>1.066399788E9</v>
+        <v>1.066395345E9</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="25">
@@ -3066,16 +3068,16 @@
         <v>7</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="D25" s="3">
-        <v>-6.230659037E9</v>
+        <v>-6.225310573E9</v>
       </c>
       <c r="E25" s="3">
-        <v>1.066399788E9</v>
+        <v>1.066381267E9</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="26">
@@ -3086,16 +3088,16 @@
         <v>7</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="D26" s="3">
-        <v>-6.233593294E9</v>
+        <v>-6.223479495E9</v>
       </c>
       <c r="E26" s="3">
-        <v>1.066323963E9</v>
+        <v>1.066424764E9</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="27">
@@ -3106,16 +3108,16 @@
         <v>7</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="D27" s="3">
-        <v>-6.227639166E9</v>
+        <v>-6.2219482E7</v>
       </c>
       <c r="E27" s="3">
-        <v>1.066395435E9</v>
+        <v>1.066463751E9</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="28">
@@ -3126,16 +3128,16 @@
         <v>7</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="D28" s="3">
-        <v>-6.227639166E9</v>
+        <v>-6.220661565E9</v>
       </c>
       <c r="E28" s="3">
-        <v>1.066395435E9</v>
+        <v>1.06650103E8</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="29">
@@ -3146,13 +3148,13 @@
         <v>7</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="D29" s="3">
-        <v>-6.233502337E9</v>
+        <v>-6.220051508E9</v>
       </c>
       <c r="E29" s="3">
-        <v>1.066325677E9</v>
+        <v>1.066543389E9</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>11</v>
@@ -3163,16 +3165,16 @@
         <v>6</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>7</v>
+        <v>38</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="D30" s="3">
-        <v>-6.225292264E9</v>
+        <v>-622095.0</v>
       </c>
       <c r="E30" s="3">
-        <v>1.066381989E9</v>
+        <v>1066588.0</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>9</v>
@@ -3183,16 +3185,16 @@
         <v>6</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>7</v>
+        <v>38</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="D31" s="3">
-        <v>-6.225292264E9</v>
+        <v>-6220717.0</v>
       </c>
       <c r="E31" s="3">
-        <v>1.066381989E9</v>
+        <v>1.06662567E8</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>9</v>
@@ -3203,16 +3205,16 @@
         <v>6</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>7</v>
+        <v>38</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="D32" s="3">
-        <v>-6.229564549E9</v>
+        <v>-6221.0</v>
       </c>
       <c r="E32" s="3">
-        <v>1.06633938E8</v>
+        <v>1.06666433E8</v>
       </c>
       <c r="F32" s="2" t="s">
         <v>9</v>
@@ -3223,16 +3225,16 @@
         <v>6</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>7</v>
+        <v>38</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="D33" s="3">
-        <v>-6.223488847E9</v>
+        <v>-6218033.0</v>
       </c>
       <c r="E33" s="3">
-        <v>1.06642377E8</v>
+        <v>1.06652533E8</v>
       </c>
       <c r="F33" s="2" t="s">
         <v>9</v>
@@ -3243,16 +3245,16 @@
         <v>6</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>7</v>
+        <v>38</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="D34" s="3">
-        <v>-6.223488847E9</v>
+        <v>-6216667.0</v>
       </c>
       <c r="E34" s="3">
-        <v>1.06642377E8</v>
+        <v>1.06672583E8</v>
       </c>
       <c r="F34" s="2" t="s">
         <v>9</v>
@@ -3263,19 +3265,19 @@
         <v>6</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>7</v>
+        <v>38</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="D35" s="3">
-        <v>-6.229491928E9</v>
+        <v>-6215567.0</v>
       </c>
       <c r="E35" s="3">
-        <v>1.066340282E9</v>
+        <v>1.0667665E7</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="36">
@@ -3283,16 +3285,16 @@
         <v>6</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>7</v>
+        <v>38</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="D36" s="3">
-        <v>-6.221957552E9</v>
+        <v>-621465.0</v>
       </c>
       <c r="E36" s="3">
-        <v>1.066462758E9</v>
+        <v>1.06679867E8</v>
       </c>
       <c r="F36" s="2" t="s">
         <v>9</v>
@@ -3303,19 +3305,19 @@
         <v>6</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>7</v>
+        <v>38</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="D37" s="3">
-        <v>-6.221957552E9</v>
+        <v>-6.2209782E7</v>
       </c>
       <c r="E37" s="3">
-        <v>1.066462758E9</v>
+        <v>1.066588307E9</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="38">
@@ -3323,19 +3325,19 @@
         <v>6</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>7</v>
+        <v>38</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>19</v>
+        <v>47</v>
       </c>
       <c r="D38" s="3">
-        <v>-6.229744972E9</v>
+        <v>-6.22072222E8</v>
       </c>
       <c r="E38" s="3">
-        <v>1.066369928E9</v>
+        <v>1.066627778E9</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="39">
@@ -3343,19 +3345,19 @@
         <v>6</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>7</v>
+        <v>38</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="D39" s="3">
-        <v>-6.220661734E9</v>
+        <v>-6.2209235E7</v>
       </c>
       <c r="E39" s="3">
-        <v>1.066500488E9</v>
+        <v>1.066664458E9</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="40">
@@ -3363,19 +3365,19 @@
         <v>6</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>7</v>
+        <v>38</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>28</v>
+        <v>49</v>
       </c>
       <c r="D40" s="3">
-        <v>-6.220661734E9</v>
+        <v>-6.21797222E8</v>
       </c>
       <c r="E40" s="3">
-        <v>1.066500488E9</v>
+        <v>1.066691667E9</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="41">
@@ -3383,16 +3385,16 @@
         <v>6</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>7</v>
+        <v>38</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="D41" s="3">
-        <v>-6.229754043E9</v>
+        <v>-6.21669444E8</v>
       </c>
       <c r="E41" s="3">
-        <v>1.066369838E9</v>
+        <v>1066725.0</v>
       </c>
       <c r="F41" s="2" t="s">
         <v>11</v>
@@ -3403,19 +3405,19 @@
         <v>6</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>7</v>
+        <v>38</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>30</v>
+        <v>51</v>
       </c>
       <c r="D42" s="3">
-        <v>-6.22006072E8</v>
+        <v>-6.2155865E7</v>
       </c>
       <c r="E42" s="3">
-        <v>1.066542847E9</v>
+        <v>1.066766509E9</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="43">
@@ -3423,19 +3425,19 @@
         <v>6</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>7</v>
+        <v>38</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>30</v>
+        <v>52</v>
       </c>
       <c r="D43" s="3">
-        <v>-6.22006072E8</v>
+        <v>-6.2146776E7</v>
       </c>
       <c r="E43" s="3">
-        <v>1.066542847E9</v>
+        <v>1.066798414E9</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="44">
@@ -3443,19 +3445,19 @@
         <v>6</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>7</v>
+        <v>53</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="D44" s="3">
-        <v>-6.230659037E9</v>
+        <v>-6.211541367E9</v>
       </c>
       <c r="E44" s="3">
-        <v>1.066399788E9</v>
+        <v>1.066833531E9</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="45">
@@ -3463,16 +3465,16 @@
         <v>6</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>7</v>
+        <v>53</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>10</v>
+        <v>55</v>
       </c>
       <c r="D45" s="3">
-        <v>-6.243098712E9</v>
+        <v>-6.21078631E8</v>
       </c>
       <c r="E45" s="3">
-        <v>1.066406036E9</v>
+        <v>1.066876155E9</v>
       </c>
       <c r="F45" s="2" t="s">
         <v>11</v>
@@ -3483,16 +3485,16 @@
         <v>6</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>7</v>
+        <v>53</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>10</v>
+        <v>56</v>
       </c>
       <c r="D46" s="3">
-        <v>-6.243098712E9</v>
+        <v>-6.206788028E9</v>
       </c>
       <c r="E46" s="3">
-        <v>1.066406036E9</v>
+        <v>1.066880997E9</v>
       </c>
       <c r="F46" s="2" t="s">
         <v>11</v>
@@ -3503,16 +3505,16 @@
         <v>6</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>7</v>
+        <v>53</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>31</v>
+        <v>57</v>
       </c>
       <c r="D47" s="3">
-        <v>-6.230677813E9</v>
+        <v>-6.202373687E9</v>
       </c>
       <c r="E47" s="3">
-        <v>1.066399892E9</v>
+        <v>1.066886187E9</v>
       </c>
       <c r="F47" s="2" t="s">
         <v>11</v>
@@ -3523,16 +3525,16 @@
         <v>6</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>7</v>
+        <v>53</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>14</v>
+        <v>58</v>
       </c>
       <c r="D48" s="3">
-        <v>-6.241009205E9</v>
+        <v>-6.199876709E9</v>
       </c>
       <c r="E48" s="3">
-        <v>1.066379133E9</v>
+        <v>1.066918545E9</v>
       </c>
       <c r="F48" s="2" t="s">
         <v>11</v>
@@ -3543,16 +3545,16 @@
         <v>6</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>7</v>
+        <v>53</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>14</v>
+        <v>59</v>
       </c>
       <c r="D49" s="3">
-        <v>-6.241009205E9</v>
+        <v>-6.199402067E9</v>
       </c>
       <c r="E49" s="3">
-        <v>1.066379133E9</v>
+        <v>1.066960725E9</v>
       </c>
       <c r="F49" s="2" t="s">
         <v>11</v>
@@ -3563,19 +3565,19 @@
         <v>6</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>7</v>
+        <v>53</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>22</v>
+        <v>60</v>
       </c>
       <c r="D50" s="3">
-        <v>-6.227639166E9</v>
+        <v>-6.197646841E9</v>
       </c>
       <c r="E50" s="3">
-        <v>1.066395435E9</v>
+        <v>1.066992112E9</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="51">
@@ -3583,16 +3585,16 @@
         <v>6</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>7</v>
+        <v>53</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>17</v>
+        <v>61</v>
       </c>
       <c r="D51" s="3">
-        <v>-6.23893105E8</v>
+        <v>-6.195070846E9</v>
       </c>
       <c r="E51" s="3">
-        <v>1.066344731E9</v>
+        <v>1.067016967E9</v>
       </c>
       <c r="F51" s="2" t="s">
         <v>11</v>
@@ -3603,16 +3605,16 @@
         <v>6</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>7</v>
+        <v>53</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>17</v>
+        <v>62</v>
       </c>
       <c r="D52" s="3">
-        <v>-6.23893105E8</v>
+        <v>-6.197910124E9</v>
       </c>
       <c r="E52" s="3">
-        <v>1.066344731E9</v>
+        <v>1.067045157E9</v>
       </c>
       <c r="F52" s="2" t="s">
         <v>11</v>
@@ -3623,16 +3625,16 @@
         <v>6</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>7</v>
+        <v>53</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>32</v>
+        <v>63</v>
       </c>
       <c r="D53" s="3">
-        <v>-6.227648237E9</v>
+        <v>-61975.0</v>
       </c>
       <c r="E53" s="3">
-        <v>1.066395345E9</v>
+        <v>1067072.0</v>
       </c>
       <c r="F53" s="2" t="s">
         <v>11</v>
@@ -3643,19 +3645,19 @@
         <v>6</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>7</v>
+        <v>64</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>20</v>
+        <v>65</v>
       </c>
       <c r="D54" s="3">
-        <v>-6.237594186E9</v>
+        <v>-6.21145944E8</v>
       </c>
       <c r="E54" s="3">
-        <v>1.066310893E9</v>
+        <v>1.066835245E9</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="55">
@@ -3663,19 +3665,19 @@
         <v>6</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>7</v>
+        <v>64</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>20</v>
+        <v>66</v>
       </c>
       <c r="D55" s="3">
-        <v>-6.237594186E9</v>
+        <v>-6.210767534E9</v>
       </c>
       <c r="E55" s="3">
-        <v>1.066310893E9</v>
+        <v>1.066878323E9</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="56">
@@ -3683,16 +3685,16 @@
         <v>6</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>7</v>
+        <v>64</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="D56" s="3">
-        <v>-6.225292264E9</v>
+        <v>-6.206770347E9</v>
       </c>
       <c r="E56" s="3">
-        <v>1.066381989E9</v>
+        <v>1.066879731E9</v>
       </c>
       <c r="F56" s="2" t="s">
         <v>9</v>
@@ -3703,19 +3705,19 @@
         <v>6</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C57" s="2" t="s">
-        <v>23</v>
+        <v>64</v>
+      </c>
+      <c r="C57" s="4" t="s">
+        <v>68</v>
       </c>
       <c r="D57" s="3">
-        <v>-6.233502337E9</v>
+        <v>-6.202138299E9</v>
       </c>
       <c r="E57" s="3">
-        <v>1.066325677E9</v>
+        <v>1.066887083E9</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="58">
@@ -3723,19 +3725,19 @@
         <v>6</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C58" s="2" t="s">
-        <v>23</v>
+        <v>64</v>
+      </c>
+      <c r="C58" s="4" t="s">
+        <v>69</v>
       </c>
       <c r="D58" s="3">
-        <v>-6.233502337E9</v>
+        <v>-6.199785161E9</v>
       </c>
       <c r="E58" s="3">
-        <v>1.066325677E9</v>
+        <v>1.066922066E9</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="59">
@@ -3743,19 +3745,19 @@
         <v>6</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C59" s="2" t="s">
-        <v>33</v>
+        <v>64</v>
+      </c>
+      <c r="C59" s="4" t="s">
+        <v>70</v>
       </c>
       <c r="D59" s="3">
-        <v>-6.225310573E9</v>
+        <v>-6.199473566E9</v>
       </c>
       <c r="E59" s="3">
-        <v>1.066381267E9</v>
+        <v>1.066963347E9</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="60">
@@ -3763,19 +3765,19 @@
         <v>6</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C60" s="2" t="s">
-        <v>26</v>
+        <v>64</v>
+      </c>
+      <c r="C60" s="4" t="s">
+        <v>71</v>
       </c>
       <c r="D60" s="3">
-        <v>-6.229491928E9</v>
+        <v>-6.197312075E9</v>
       </c>
       <c r="E60" s="3">
-        <v>1.066340282E9</v>
+        <v>1.066992734E9</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="61">
@@ -3783,19 +3785,19 @@
         <v>6</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C61" s="2" t="s">
-        <v>26</v>
+        <v>64</v>
+      </c>
+      <c r="C61" s="4" t="s">
+        <v>72</v>
       </c>
       <c r="D61" s="3">
-        <v>-6.229491928E9</v>
+        <v>-6.195070643E9</v>
       </c>
       <c r="E61" s="3">
-        <v>1.066340282E9</v>
+        <v>1.067017599E9</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="62">
@@ -3803,16 +3805,16 @@
         <v>6</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C62" s="2" t="s">
-        <v>25</v>
+        <v>64</v>
+      </c>
+      <c r="C62" s="4" t="s">
+        <v>73</v>
       </c>
       <c r="D62" s="3">
-        <v>-6.223488847E9</v>
+        <v>-6.197810282E9</v>
       </c>
       <c r="E62" s="3">
-        <v>1.06642377E8</v>
+        <v>1.067046329E9</v>
       </c>
       <c r="F62" s="2" t="s">
         <v>9</v>
@@ -3823,19 +3825,19 @@
         <v>6</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C63" s="2" t="s">
-        <v>29</v>
+        <v>64</v>
+      </c>
+      <c r="C63" s="4" t="s">
+        <v>74</v>
       </c>
       <c r="D63" s="3">
-        <v>-6.229754043E9</v>
+        <v>-6.196307179E9</v>
       </c>
       <c r="E63" s="3">
-        <v>1.066369838E9</v>
+        <v>1.067080886E9</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="64">
@@ -3843,19 +3845,19 @@
         <v>6</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C64" s="2" t="s">
-        <v>29</v>
+        <v>64</v>
+      </c>
+      <c r="C64" s="4" t="s">
+        <v>75</v>
       </c>
       <c r="D64" s="3">
-        <v>-6.229754043E9</v>
+        <v>-6.192330082E9</v>
       </c>
       <c r="E64" s="3">
-        <v>1.066369838E9</v>
+        <v>1.067104249E9</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="65">
@@ -3863,19 +3865,19 @@
         <v>6</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C65" s="2" t="s">
-        <v>34</v>
+        <v>64</v>
+      </c>
+      <c r="C65" s="4" t="s">
+        <v>76</v>
       </c>
       <c r="D65" s="3">
-        <v>-6.223479495E9</v>
+        <v>-6.18956417E8</v>
       </c>
       <c r="E65" s="3">
-        <v>1.066424764E9</v>
+        <v>1.067129097E9</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="66">
@@ -3883,19 +3885,19 @@
         <v>6</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C66" s="2" t="s">
-        <v>31</v>
+        <v>64</v>
+      </c>
+      <c r="C66" s="4" t="s">
+        <v>77</v>
       </c>
       <c r="D66" s="3">
-        <v>-6.230677813E9</v>
+        <v>-6.189822446E9</v>
       </c>
       <c r="E66" s="3">
-        <v>1.066399892E9</v>
+        <v>1.067169312E9</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="67">
@@ -3903,19 +3905,19 @@
         <v>6</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C67" s="2" t="s">
-        <v>31</v>
+        <v>78</v>
+      </c>
+      <c r="C67" s="4" t="s">
+        <v>79</v>
       </c>
       <c r="D67" s="3">
-        <v>-6.230677813E9</v>
+        <v>-6.171664475E9</v>
       </c>
       <c r="E67" s="3">
-        <v>1.066399892E9</v>
+        <v>1.067277327E9</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="68">
@@ -3923,19 +3925,19 @@
         <v>6</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C68" s="2" t="s">
-        <v>27</v>
+        <v>78</v>
+      </c>
+      <c r="C68" s="4" t="s">
+        <v>79</v>
       </c>
       <c r="D68" s="3">
-        <v>-6.221957552E9</v>
+        <v>-6.171664475E9</v>
       </c>
       <c r="E68" s="3">
-        <v>1.066462758E9</v>
+        <v>1.067277327E9</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="69">
@@ -3943,19 +3945,19 @@
         <v>6</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C69" s="2" t="s">
-        <v>32</v>
+        <v>78</v>
+      </c>
+      <c r="C69" s="4" t="s">
+        <v>80</v>
       </c>
       <c r="D69" s="3">
-        <v>-6.227648237E9</v>
+        <v>-6.175182254E9</v>
       </c>
       <c r="E69" s="3">
-        <v>1.066395345E9</v>
+        <v>1.067279483E9</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="70">
@@ -3963,16 +3965,16 @@
         <v>6</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C70" s="2" t="s">
-        <v>32</v>
+        <v>78</v>
+      </c>
+      <c r="C70" s="4" t="s">
+        <v>80</v>
       </c>
       <c r="D70" s="3">
-        <v>-6.227648237E9</v>
+        <v>-6.175182254E9</v>
       </c>
       <c r="E70" s="3">
-        <v>1.066395345E9</v>
+        <v>1.067279483E9</v>
       </c>
       <c r="F70" s="2" t="s">
         <v>11</v>
@@ -3983,19 +3985,19 @@
         <v>6</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C71" s="2" t="s">
-        <v>35</v>
+        <v>78</v>
+      </c>
+      <c r="C71" s="4" t="s">
+        <v>81</v>
       </c>
       <c r="D71" s="3">
-        <v>-6.2219482E7</v>
+        <v>-6.17816597E8</v>
       </c>
       <c r="E71" s="3">
-        <v>1.066463751E9</v>
+        <v>1.067282659E9</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="72">
@@ -4003,16 +4005,16 @@
         <v>6</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C72" s="2" t="s">
-        <v>33</v>
+        <v>78</v>
+      </c>
+      <c r="C72" s="4" t="s">
+        <v>81</v>
       </c>
       <c r="D72" s="3">
-        <v>-6.225310573E9</v>
+        <v>-6.17816597E8</v>
       </c>
       <c r="E72" s="3">
-        <v>1.066381267E9</v>
+        <v>1.067282659E9</v>
       </c>
       <c r="F72" s="2" t="s">
         <v>11</v>
@@ -4023,19 +4025,19 @@
         <v>6</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C73" s="2" t="s">
-        <v>33</v>
+        <v>78</v>
+      </c>
+      <c r="C73" s="4" t="s">
+        <v>82</v>
       </c>
       <c r="D73" s="3">
-        <v>-6.225310573E9</v>
+        <v>-6.181522685E9</v>
       </c>
       <c r="E73" s="3">
-        <v>1.066381267E9</v>
+        <v>1.06728885E8</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="74">
@@ -4043,19 +4045,19 @@
         <v>6</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C74" s="2" t="s">
-        <v>28</v>
+        <v>78</v>
+      </c>
+      <c r="C74" s="4" t="s">
+        <v>82</v>
       </c>
       <c r="D74" s="3">
-        <v>-6.220661734E9</v>
+        <v>-6.181522685E9</v>
       </c>
       <c r="E74" s="3">
-        <v>1.066500488E9</v>
+        <v>1.06728885E8</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="75">
@@ -4063,19 +4065,19 @@
         <v>6</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C75" s="2" t="s">
-        <v>34</v>
+        <v>78</v>
+      </c>
+      <c r="C75" s="4" t="s">
+        <v>83</v>
       </c>
       <c r="D75" s="3">
-        <v>-6.223479495E9</v>
+        <v>-6.184816972E9</v>
       </c>
       <c r="E75" s="3">
-        <v>1.066424764E9</v>
+        <v>1.067297078E9</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="76">
@@ -4083,16 +4085,16 @@
         <v>6</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C76" s="2" t="s">
-        <v>34</v>
+        <v>78</v>
+      </c>
+      <c r="C76" s="4" t="s">
+        <v>83</v>
       </c>
       <c r="D76" s="3">
-        <v>-6.223479495E9</v>
+        <v>-6.184816972E9</v>
       </c>
       <c r="E76" s="3">
-        <v>1.066424764E9</v>
+        <v>1.067297078E9</v>
       </c>
       <c r="F76" s="2" t="s">
         <v>11</v>
@@ -4103,19 +4105,19 @@
         <v>6</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C77" s="2" t="s">
-        <v>36</v>
+        <v>78</v>
+      </c>
+      <c r="C77" s="4" t="s">
+        <v>84</v>
       </c>
       <c r="D77" s="3">
-        <v>-6.220661565E9</v>
+        <v>-6.185604862E9</v>
       </c>
       <c r="E77" s="3">
-        <v>1.06650103E8</v>
+        <v>1.067268604E9</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="78">
@@ -4123,16 +4125,16 @@
         <v>6</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C78" s="2" t="s">
-        <v>35</v>
+        <v>78</v>
+      </c>
+      <c r="C78" s="4" t="s">
+        <v>84</v>
       </c>
       <c r="D78" s="3">
-        <v>-6.2219482E7</v>
+        <v>-6.185604862E9</v>
       </c>
       <c r="E78" s="3">
-        <v>1.066463751E9</v>
+        <v>1.067268604E9</v>
       </c>
       <c r="F78" s="2" t="s">
         <v>11</v>
@@ -4143,19 +4145,19 @@
         <v>6</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C79" s="2" t="s">
-        <v>35</v>
+        <v>78</v>
+      </c>
+      <c r="C79" s="4" t="s">
+        <v>85</v>
       </c>
       <c r="D79" s="3">
-        <v>-6.2219482E7</v>
+        <v>-6.187218306E9</v>
       </c>
       <c r="E79" s="3">
-        <v>1.066463751E9</v>
+        <v>1.067241545E9</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="80">
@@ -4163,19 +4165,19 @@
         <v>6</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C80" s="2" t="s">
-        <v>30</v>
+        <v>78</v>
+      </c>
+      <c r="C80" s="4" t="s">
+        <v>85</v>
       </c>
       <c r="D80" s="3">
-        <v>-6.22006072E8</v>
+        <v>-6.187218306E9</v>
       </c>
       <c r="E80" s="3">
-        <v>1.066542847E9</v>
+        <v>1.067241545E9</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="81">
@@ -4183,19 +4185,19 @@
         <v>6</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C81" s="2" t="s">
-        <v>36</v>
+        <v>78</v>
+      </c>
+      <c r="C81" s="4" t="s">
+        <v>86</v>
       </c>
       <c r="D81" s="3">
-        <v>-6.220661565E9</v>
+        <v>-6.188080812E9</v>
       </c>
       <c r="E81" s="3">
-        <v>1.06650103E8</v>
+        <v>1.067212383E9</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="82">
@@ -4203,16 +4205,16 @@
         <v>6</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C82" s="2" t="s">
-        <v>36</v>
+        <v>78</v>
+      </c>
+      <c r="C82" s="4" t="s">
+        <v>86</v>
       </c>
       <c r="D82" s="3">
-        <v>-6.220661565E9</v>
+        <v>-6.188080812E9</v>
       </c>
       <c r="E82" s="3">
-        <v>1.06650103E8</v>
+        <v>1.067212383E9</v>
       </c>
       <c r="F82" s="2" t="s">
         <v>11</v>
@@ -4223,19 +4225,19 @@
         <v>6</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C83" s="2" t="s">
-        <v>37</v>
+        <v>87</v>
+      </c>
+      <c r="C83" s="4" t="s">
+        <v>88</v>
       </c>
       <c r="D83" s="3">
-        <v>-6.220051508E9</v>
+        <v>-6.187582823E9</v>
       </c>
       <c r="E83" s="3">
-        <v>1.066543389E9</v>
+        <v>1.067224502E9</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="84">
@@ -4243,16 +4245,16 @@
         <v>6</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C84" s="2" t="s">
-        <v>37</v>
+        <v>87</v>
+      </c>
+      <c r="C84" s="4" t="s">
+        <v>89</v>
       </c>
       <c r="D84" s="3">
-        <v>-6.220051508E9</v>
+        <v>-6.187630789E9</v>
       </c>
       <c r="E84" s="3">
-        <v>1.066543389E9</v>
+        <v>1.067226349E9</v>
       </c>
       <c r="F84" s="2" t="s">
         <v>11</v>
@@ -4263,19 +4265,19 @@
         <v>6</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C85" s="2" t="s">
-        <v>37</v>
+        <v>87</v>
+      </c>
+      <c r="C85" s="4" t="s">
+        <v>90</v>
       </c>
       <c r="D85" s="3">
-        <v>-6.220051508E9</v>
+        <v>-6.186596818E9</v>
       </c>
       <c r="E85" s="3">
-        <v>1.066543389E9</v>
+        <v>1.067251902E9</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="86">
@@ -4283,16 +4285,16 @@
         <v>6</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C86" s="2" t="s">
-        <v>39</v>
+        <v>87</v>
+      </c>
+      <c r="C86" s="4" t="s">
+        <v>91</v>
       </c>
       <c r="D86" s="3">
-        <v>-622095.0</v>
+        <v>-6.185564703E9</v>
       </c>
       <c r="E86" s="3">
-        <v>1066588.0</v>
+        <v>1.067267146E9</v>
       </c>
       <c r="F86" s="2" t="s">
         <v>9</v>
@@ -4303,19 +4305,19 @@
         <v>6</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C87" s="2" t="s">
-        <v>39</v>
+        <v>87</v>
+      </c>
+      <c r="C87" s="4" t="s">
+        <v>92</v>
       </c>
       <c r="D87" s="3">
-        <v>-622095.0</v>
+        <v>-6.186615412E9</v>
       </c>
       <c r="E87" s="3">
-        <v>1066588.0</v>
+        <v>1.067253364E9</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="88">
@@ -4323,16 +4325,16 @@
         <v>6</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C88" s="2" t="s">
-        <v>40</v>
+        <v>87</v>
+      </c>
+      <c r="C88" s="4" t="s">
+        <v>93</v>
       </c>
       <c r="D88" s="3">
-        <v>-6220717.0</v>
+        <v>-6.185753257E9</v>
       </c>
       <c r="E88" s="3">
-        <v>1.06662567E8</v>
+        <v>1.067302106E9</v>
       </c>
       <c r="F88" s="2" t="s">
         <v>9</v>
@@ -4343,16 +4345,16 @@
         <v>6</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C89" s="2" t="s">
-        <v>40</v>
+        <v>87</v>
+      </c>
+      <c r="C89" s="4" t="s">
+        <v>94</v>
       </c>
       <c r="D89" s="3">
-        <v>-6220717.0</v>
+        <v>-6.189565202E9</v>
       </c>
       <c r="E89" s="3">
-        <v>1.06662567E8</v>
+        <v>1.067298684E9</v>
       </c>
       <c r="F89" s="2" t="s">
         <v>9</v>
@@ -4363,19 +4365,19 @@
         <v>6</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C90" s="2" t="s">
-        <v>41</v>
+        <v>87</v>
+      </c>
+      <c r="C90" s="4" t="s">
+        <v>95</v>
       </c>
       <c r="D90" s="3">
-        <v>-6221.0</v>
+        <v>-6.185558707E9</v>
       </c>
       <c r="E90" s="3">
-        <v>1.06666433E8</v>
+        <v>1.067268494E9</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="91">
@@ -4383,19 +4385,19 @@
         <v>6</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C91" s="2" t="s">
-        <v>41</v>
+        <v>87</v>
+      </c>
+      <c r="C91" s="4" t="s">
+        <v>96</v>
       </c>
       <c r="D91" s="3">
-        <v>-6221.0</v>
+        <v>-6.185765988E9</v>
       </c>
       <c r="E91" s="3">
-        <v>1.06666433E8</v>
+        <v>1.067301557E9</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="92">
@@ -4403,19 +4405,19 @@
         <v>6</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C92" s="2" t="s">
-        <v>42</v>
+        <v>87</v>
+      </c>
+      <c r="C92" s="4" t="s">
+        <v>97</v>
       </c>
       <c r="D92" s="3">
-        <v>-6218033.0</v>
+        <v>-6.189551826E9</v>
       </c>
       <c r="E92" s="3">
-        <v>1.06652533E8</v>
+        <v>1.067298209E9</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="93">
@@ -4423,19 +4425,19 @@
         <v>6</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C93" s="2" t="s">
-        <v>42</v>
+        <v>98</v>
+      </c>
+      <c r="C93" s="4" t="s">
+        <v>99</v>
       </c>
       <c r="D93" s="3">
-        <v>-6218033.0</v>
+        <v>-6.196451622E9</v>
       </c>
       <c r="E93" s="3">
-        <v>1.06652533E8</v>
+        <v>1.067081613E9</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="94">
@@ -4443,19 +4445,19 @@
         <v>6</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C94" s="2" t="s">
-        <v>43</v>
+        <v>98</v>
+      </c>
+      <c r="C94" s="4" t="s">
+        <v>100</v>
       </c>
       <c r="D94" s="3">
-        <v>-6216667.0</v>
+        <v>-6.192492899E9</v>
       </c>
       <c r="E94" s="3">
-        <v>1.06672583E8</v>
+        <v>1.067104074E9</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="95">
@@ -4463,19 +4465,19 @@
         <v>6</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C95" s="2" t="s">
-        <v>43</v>
+        <v>98</v>
+      </c>
+      <c r="C95" s="4" t="s">
+        <v>101</v>
       </c>
       <c r="D95" s="3">
-        <v>-6216667.0</v>
+        <v>-6.189609031E9</v>
       </c>
       <c r="E95" s="3">
-        <v>1.06672583E8</v>
+        <v>1.067130183E9</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="96">
@@ -4483,19 +4485,19 @@
         <v>6</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C96" s="2" t="s">
-        <v>44</v>
+        <v>98</v>
+      </c>
+      <c r="C96" s="4" t="s">
+        <v>102</v>
       </c>
       <c r="D96" s="3">
-        <v>-6215567.0</v>
+        <v>-6.1898949E7</v>
       </c>
       <c r="E96" s="3">
-        <v>1.0667665E7</v>
+        <v>1.067168953E9</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="97">
@@ -4503,19 +4505,19 @@
         <v>6</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C97" s="2" t="s">
-        <v>44</v>
+        <v>98</v>
+      </c>
+      <c r="C97" s="4" t="s">
+        <v>103</v>
       </c>
       <c r="D97" s="3">
-        <v>-6215567.0</v>
+        <v>-61972.0</v>
       </c>
       <c r="E97" s="3">
-        <v>1.0667665E7</v>
+        <v>1067067.0</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="98">
@@ -4523,16 +4525,16 @@
         <v>6</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C98" s="2" t="s">
-        <v>45</v>
+        <v>104</v>
+      </c>
+      <c r="C98" s="4" t="s">
+        <v>105</v>
       </c>
       <c r="D98" s="3">
-        <v>-621465.0</v>
+        <v>-6.245096996E9</v>
       </c>
       <c r="E98" s="3">
-        <v>1.06679867E8</v>
+        <v>1.06611612E8</v>
       </c>
       <c r="F98" s="2" t="s">
         <v>9</v>
@@ -4543,16 +4545,16 @@
         <v>6</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C99" s="2" t="s">
-        <v>45</v>
+        <v>104</v>
+      </c>
+      <c r="C99" s="4" t="s">
+        <v>106</v>
       </c>
       <c r="D99" s="3">
-        <v>-621465.0</v>
+        <v>-6.243126004E9</v>
       </c>
       <c r="E99" s="3">
-        <v>1.06679867E8</v>
+        <v>1.06616485E8</v>
       </c>
       <c r="F99" s="2" t="s">
         <v>9</v>
@@ -4563,19 +4565,19 @@
         <v>6</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C100" s="2" t="s">
-        <v>46</v>
+        <v>104</v>
+      </c>
+      <c r="C100" s="4" t="s">
+        <v>107</v>
       </c>
       <c r="D100" s="3">
-        <v>-6.2209782E7</v>
+        <v>-6.242830004E9</v>
       </c>
       <c r="E100" s="3">
-        <v>1.066588307E9</v>
+        <v>1.06621432E8</v>
       </c>
       <c r="F100" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="101">
@@ -4583,19 +4585,19 @@
         <v>6</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C101" s="2" t="s">
-        <v>46</v>
+        <v>104</v>
+      </c>
+      <c r="C101" s="4" t="s">
+        <v>108</v>
       </c>
       <c r="D101" s="3">
-        <v>-6.2209782E7</v>
+        <v>-6.242863001E9</v>
       </c>
       <c r="E101" s="3">
-        <v>1.066588307E9</v>
+        <v>1.06625613E8</v>
       </c>
       <c r="F101" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="102">
@@ -4603,19 +4605,19 @@
         <v>6</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C102" s="2" t="s">
-        <v>47</v>
+        <v>104</v>
+      </c>
+      <c r="C102" s="4" t="s">
+        <v>109</v>
       </c>
       <c r="D102" s="3">
-        <v>-6.22072222E8</v>
+        <v>-6.243502005E9</v>
       </c>
       <c r="E102" s="3">
-        <v>1.066627778E9</v>
+        <v>1.06631477E8</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="103">
@@ -4623,19 +4625,19 @@
         <v>6</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C103" s="2" t="s">
-        <v>47</v>
+        <v>104</v>
+      </c>
+      <c r="C103" s="4" t="s">
+        <v>110</v>
       </c>
       <c r="D103" s="3">
-        <v>-6.22072222E8</v>
+        <v>-6245455.0</v>
       </c>
       <c r="E103" s="3">
-        <v>1.066627778E9</v>
+        <v>1.06634934E8</v>
       </c>
       <c r="F103" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="104">
@@ -4643,19 +4645,19 @@
         <v>6</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C104" s="2" t="s">
-        <v>48</v>
+        <v>104</v>
+      </c>
+      <c r="C104" s="4" t="s">
+        <v>111</v>
       </c>
       <c r="D104" s="3">
-        <v>-6.2209235E7</v>
+        <v>-6.243185999E9</v>
       </c>
       <c r="E104" s="3">
-        <v>1.066664458E9</v>
+        <v>1.06637889E8</v>
       </c>
       <c r="F104" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="105">
@@ -4663,19 +4665,19 @@
         <v>6</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C105" s="2" t="s">
-        <v>48</v>
+        <v>104</v>
+      </c>
+      <c r="C105" s="4" t="s">
+        <v>112</v>
       </c>
       <c r="D105" s="3">
-        <v>-6.2209235E7</v>
+        <v>-6.243172998E9</v>
       </c>
       <c r="E105" s="3">
-        <v>1.066664458E9</v>
+        <v>1.06640725E8</v>
       </c>
       <c r="F105" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="106">
@@ -4683,16 +4685,16 @@
         <v>6</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C106" s="2" t="s">
-        <v>49</v>
+        <v>104</v>
+      </c>
+      <c r="C106" s="4" t="s">
+        <v>113</v>
       </c>
       <c r="D106" s="3">
-        <v>-6.21797222E8</v>
+        <v>-6.245195004E9</v>
       </c>
       <c r="E106" s="3">
-        <v>1.066691667E9</v>
+        <v>1.06611803E8</v>
       </c>
       <c r="F106" s="2" t="s">
         <v>11</v>
@@ -4703,16 +4705,16 @@
         <v>6</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C107" s="2" t="s">
-        <v>49</v>
+        <v>104</v>
+      </c>
+      <c r="C107" s="4" t="s">
+        <v>114</v>
       </c>
       <c r="D107" s="3">
-        <v>-6.21797222E8</v>
+        <v>-6243258.0</v>
       </c>
       <c r="E107" s="3">
-        <v>1.066691667E9</v>
+        <v>1.06616915E8</v>
       </c>
       <c r="F107" s="2" t="s">
         <v>11</v>
@@ -4723,16 +4725,16 @@
         <v>6</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C108" s="2" t="s">
-        <v>50</v>
+        <v>104</v>
+      </c>
+      <c r="C108" s="4" t="s">
+        <v>115</v>
       </c>
       <c r="D108" s="3">
-        <v>-6.21669444E8</v>
+        <v>-6.242779998E9</v>
       </c>
       <c r="E108" s="3">
-        <v>1066725.0</v>
+        <v>1.06621805E8</v>
       </c>
       <c r="F108" s="2" t="s">
         <v>11</v>
@@ -4743,16 +4745,16 @@
         <v>6</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C109" s="2" t="s">
-        <v>50</v>
+        <v>104</v>
+      </c>
+      <c r="C109" s="4" t="s">
+        <v>116</v>
       </c>
       <c r="D109" s="3">
-        <v>-6.21669444E8</v>
+        <v>-6.242945997E9</v>
       </c>
       <c r="E109" s="3">
-        <v>1066725.0</v>
+        <v>1.06625858E8</v>
       </c>
       <c r="F109" s="2" t="s">
         <v>11</v>
@@ -4763,16 +4765,16 @@
         <v>6</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C110" s="2" t="s">
-        <v>51</v>
+        <v>104</v>
+      </c>
+      <c r="C110" s="4" t="s">
+        <v>117</v>
       </c>
       <c r="D110" s="3">
-        <v>-6.2155865E7</v>
+        <v>-6.243495999E9</v>
       </c>
       <c r="E110" s="3">
-        <v>1.066766509E9</v>
+        <v>1.06631177E8</v>
       </c>
       <c r="F110" s="2" t="s">
         <v>11</v>
@@ -4783,16 +4785,16 @@
         <v>6</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C111" s="2" t="s">
-        <v>51</v>
+        <v>104</v>
+      </c>
+      <c r="C111" s="4" t="s">
+        <v>118</v>
       </c>
       <c r="D111" s="3">
-        <v>-6.2155865E7</v>
+        <v>-6.245406004E9</v>
       </c>
       <c r="E111" s="3">
-        <v>1.066766509E9</v>
+        <v>1.06634705E8</v>
       </c>
       <c r="F111" s="2" t="s">
         <v>11</v>
@@ -4803,16 +4805,16 @@
         <v>6</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C112" s="2" t="s">
-        <v>52</v>
+        <v>104</v>
+      </c>
+      <c r="C112" s="4" t="s">
+        <v>119</v>
       </c>
       <c r="D112" s="3">
-        <v>-6.2146776E7</v>
+        <v>-6.242610997E9</v>
       </c>
       <c r="E112" s="3">
-        <v>1.066798414E9</v>
+        <v>1.06638267E8</v>
       </c>
       <c r="F112" s="2" t="s">
         <v>11</v>
@@ -4823,4502 +4825,23 @@
         <v>6</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C113" s="2" t="s">
-        <v>52</v>
+        <v>104</v>
+      </c>
+      <c r="C113" s="4" t="s">
+        <v>120</v>
       </c>
       <c r="D113" s="3">
-        <v>-6.2146776E7</v>
+        <v>-6.243172998E9</v>
       </c>
       <c r="E113" s="3">
-        <v>1.066798414E9</v>
+        <v>1.06640725E8</v>
       </c>
       <c r="F113" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="114">
-      <c r="A114" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B114" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C114" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D114" s="3">
-        <v>-6.2209782E7</v>
-      </c>
-      <c r="E114" s="3">
-        <v>1.066588307E9</v>
-      </c>
-      <c r="F114" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B115" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C115" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="D115" s="3">
-        <v>-6.22072222E8</v>
-      </c>
-      <c r="E115" s="3">
-        <v>1.066627778E9</v>
-      </c>
-      <c r="F115" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B116" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C116" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="D116" s="3">
-        <v>-6.2209235E7</v>
-      </c>
-      <c r="E116" s="3">
-        <v>1.066664458E9</v>
-      </c>
-      <c r="F116" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B117" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C117" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="D117" s="3">
-        <v>-6.21797222E8</v>
-      </c>
-      <c r="E117" s="3">
-        <v>1.066691667E9</v>
-      </c>
-      <c r="F117" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B118" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C118" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="D118" s="3">
-        <v>-6.21669444E8</v>
-      </c>
-      <c r="E118" s="3">
-        <v>1066725.0</v>
-      </c>
-      <c r="F118" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B119" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C119" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="D119" s="3">
-        <v>-6.2155865E7</v>
-      </c>
-      <c r="E119" s="3">
-        <v>1.066766509E9</v>
-      </c>
-      <c r="F119" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B120" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C120" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="D120" s="3">
-        <v>-6.2146776E7</v>
-      </c>
-      <c r="E120" s="3">
-        <v>1.066798414E9</v>
-      </c>
-      <c r="F120" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B121" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C121" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="D121" s="3">
-        <v>-622095.0</v>
-      </c>
-      <c r="E121" s="3">
-        <v>1066588.0</v>
-      </c>
-      <c r="F121" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B122" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C122" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="D122" s="3">
-        <v>-6220717.0</v>
-      </c>
-      <c r="E122" s="3">
-        <v>1.06662567E8</v>
-      </c>
-      <c r="F122" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B123" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C123" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="D123" s="3">
-        <v>-6221.0</v>
-      </c>
-      <c r="E123" s="3">
-        <v>1.06666433E8</v>
-      </c>
-      <c r="F123" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B124" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C124" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="D124" s="3">
-        <v>-6218033.0</v>
-      </c>
-      <c r="E124" s="3">
-        <v>1.06652533E8</v>
-      </c>
-      <c r="F124" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B125" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C125" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="D125" s="3">
-        <v>-6216667.0</v>
-      </c>
-      <c r="E125" s="3">
-        <v>1.06672583E8</v>
-      </c>
-      <c r="F125" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B126" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C126" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="D126" s="3">
-        <v>-6215567.0</v>
-      </c>
-      <c r="E126" s="3">
-        <v>1.0667665E7</v>
-      </c>
-      <c r="F126" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B127" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C127" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="D127" s="3">
-        <v>-621465.0</v>
-      </c>
-      <c r="E127" s="3">
-        <v>1.06679867E8</v>
-      </c>
-      <c r="F127" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B128" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C128" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="D128" s="3">
-        <v>-6.211541367E9</v>
-      </c>
-      <c r="E128" s="3">
-        <v>1.066833531E9</v>
-      </c>
-      <c r="F128" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B129" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C129" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="D129" s="3">
-        <v>-6.211541367E9</v>
-      </c>
-      <c r="E129" s="3">
-        <v>1.066833531E9</v>
-      </c>
-      <c r="F129" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B130" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C130" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="D130" s="3">
-        <v>-6.21078631E8</v>
-      </c>
-      <c r="E130" s="3">
-        <v>1.066876155E9</v>
-      </c>
-      <c r="F130" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B131" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C131" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="D131" s="3">
-        <v>-6.21078631E8</v>
-      </c>
-      <c r="E131" s="3">
-        <v>1.066876155E9</v>
-      </c>
-      <c r="F131" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B132" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C132" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="D132" s="3">
-        <v>-6.206788028E9</v>
-      </c>
-      <c r="E132" s="3">
-        <v>1.066880997E9</v>
-      </c>
-      <c r="F132" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B133" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C133" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="D133" s="3">
-        <v>-6.206788028E9</v>
-      </c>
-      <c r="E133" s="3">
-        <v>1.066880997E9</v>
-      </c>
-      <c r="F133" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B134" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C134" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D134" s="3">
-        <v>-6.202373687E9</v>
-      </c>
-      <c r="E134" s="3">
-        <v>1.066886187E9</v>
-      </c>
-      <c r="F134" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B135" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C135" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D135" s="3">
-        <v>-6.202373687E9</v>
-      </c>
-      <c r="E135" s="3">
-        <v>1.066886187E9</v>
-      </c>
-      <c r="F135" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B136" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C136" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="D136" s="3">
-        <v>-6.199876709E9</v>
-      </c>
-      <c r="E136" s="3">
-        <v>1.066918545E9</v>
-      </c>
-      <c r="F136" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B137" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C137" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="D137" s="3">
-        <v>-6.199876709E9</v>
-      </c>
-      <c r="E137" s="3">
-        <v>1.066918545E9</v>
-      </c>
-      <c r="F137" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B138" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C138" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="D138" s="3">
-        <v>-6.199402067E9</v>
-      </c>
-      <c r="E138" s="3">
-        <v>1.066960725E9</v>
-      </c>
-      <c r="F138" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B139" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C139" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="D139" s="3">
-        <v>-6.199402067E9</v>
-      </c>
-      <c r="E139" s="3">
-        <v>1.066960725E9</v>
-      </c>
-      <c r="F139" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B140" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C140" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="D140" s="3">
-        <v>-6.197646841E9</v>
-      </c>
-      <c r="E140" s="3">
-        <v>1.066992112E9</v>
-      </c>
-      <c r="F140" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B141" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C141" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="D141" s="3">
-        <v>-6.197646841E9</v>
-      </c>
-      <c r="E141" s="3">
-        <v>1.066992112E9</v>
-      </c>
-      <c r="F141" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B142" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C142" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="D142" s="3">
-        <v>-6.195070846E9</v>
-      </c>
-      <c r="E142" s="3">
-        <v>1.067016967E9</v>
-      </c>
-      <c r="F142" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B143" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C143" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="D143" s="3">
-        <v>-6.195070846E9</v>
-      </c>
-      <c r="E143" s="3">
-        <v>1.067016967E9</v>
-      </c>
-      <c r="F143" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B144" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C144" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="D144" s="3">
-        <v>-6.197910124E9</v>
-      </c>
-      <c r="E144" s="3">
-        <v>1.067045157E9</v>
-      </c>
-      <c r="F144" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B145" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C145" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="D145" s="3">
-        <v>-6.197910124E9</v>
-      </c>
-      <c r="E145" s="3">
-        <v>1.067045157E9</v>
-      </c>
-      <c r="F145" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B146" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C146" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="D146" s="3">
-        <v>-61975.0</v>
-      </c>
-      <c r="E146" s="3">
-        <v>1067072.0</v>
-      </c>
-      <c r="F146" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B147" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C147" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="D147" s="3">
-        <v>-61975.0</v>
-      </c>
-      <c r="E147" s="3">
-        <v>1067072.0</v>
-      </c>
-      <c r="F147" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B148" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C148" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="D148" s="3">
-        <v>-6.211541367E9</v>
-      </c>
-      <c r="E148" s="3">
-        <v>1.066833531E9</v>
-      </c>
-      <c r="F148" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B149" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C149" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="D149" s="3">
-        <v>-6.21078631E8</v>
-      </c>
-      <c r="E149" s="3">
-        <v>1.066876155E9</v>
-      </c>
-      <c r="F149" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B150" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C150" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="D150" s="3">
-        <v>-6.206788028E9</v>
-      </c>
-      <c r="E150" s="3">
-        <v>1.066880997E9</v>
-      </c>
-      <c r="F150" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B151" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C151" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D151" s="3">
-        <v>-6.202373687E9</v>
-      </c>
-      <c r="E151" s="3">
-        <v>1.066886187E9</v>
-      </c>
-      <c r="F151" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B152" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C152" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="D152" s="3">
-        <v>-6.199876709E9</v>
-      </c>
-      <c r="E152" s="3">
-        <v>1.066918545E9</v>
-      </c>
-      <c r="F152" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B153" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C153" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="D153" s="3">
-        <v>-6.199402067E9</v>
-      </c>
-      <c r="E153" s="3">
-        <v>1.066960725E9</v>
-      </c>
-      <c r="F153" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B154" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C154" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="D154" s="3">
-        <v>-6.197646841E9</v>
-      </c>
-      <c r="E154" s="3">
-        <v>1.066992112E9</v>
-      </c>
-      <c r="F154" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B155" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C155" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="D155" s="3">
-        <v>-6.195070846E9</v>
-      </c>
-      <c r="E155" s="3">
-        <v>1.067016967E9</v>
-      </c>
-      <c r="F155" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B156" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C156" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="D156" s="3">
-        <v>-6.197910124E9</v>
-      </c>
-      <c r="E156" s="3">
-        <v>1.067045157E9</v>
-      </c>
-      <c r="F156" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B157" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C157" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="D157" s="3">
-        <v>-61975.0</v>
-      </c>
-      <c r="E157" s="3">
-        <v>1067072.0</v>
-      </c>
-      <c r="F157" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B158" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="C158" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="D158" s="3">
-        <v>-6.21145944E8</v>
-      </c>
-      <c r="E158" s="3">
-        <v>1.066835245E9</v>
-      </c>
-      <c r="F158" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B159" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="C159" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="D159" s="3">
-        <v>-6.21145944E8</v>
-      </c>
-      <c r="E159" s="3">
-        <v>1.066835245E9</v>
-      </c>
-      <c r="F159" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B160" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="C160" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="D160" s="3">
-        <v>-6.21145944E8</v>
-      </c>
-      <c r="E160" s="3">
-        <v>1.066835245E9</v>
-      </c>
-      <c r="F160" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B161" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="C161" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="D161" s="3">
-        <v>-6.210767534E9</v>
-      </c>
-      <c r="E161" s="3">
-        <v>1.066878323E9</v>
-      </c>
-      <c r="F161" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B162" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="C162" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="D162" s="3">
-        <v>-6.210767534E9</v>
-      </c>
-      <c r="E162" s="3">
-        <v>1.066878323E9</v>
-      </c>
-      <c r="F162" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B163" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="C163" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="D163" s="3">
-        <v>-6.210767534E9</v>
-      </c>
-      <c r="E163" s="3">
-        <v>1.066878323E9</v>
-      </c>
-      <c r="F163" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B164" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="C164" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="D164" s="3">
-        <v>-6.206770347E9</v>
-      </c>
-      <c r="E164" s="3">
-        <v>1.066879731E9</v>
-      </c>
-      <c r="F164" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B165" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="C165" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="D165" s="3">
-        <v>-6.206770347E9</v>
-      </c>
-      <c r="E165" s="3">
-        <v>1.066879731E9</v>
-      </c>
-      <c r="F165" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B166" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="C166" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="D166" s="3">
-        <v>-6.206770347E9</v>
-      </c>
-      <c r="E166" s="3">
-        <v>1.066879731E9</v>
-      </c>
-      <c r="F166" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B167" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="C167" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="D167" s="3">
-        <v>-6.202138299E9</v>
-      </c>
-      <c r="E167" s="3">
-        <v>1.066887083E9</v>
-      </c>
-      <c r="F167" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B168" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="C168" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="D168" s="3">
-        <v>-6.202138299E9</v>
-      </c>
-      <c r="E168" s="3">
-        <v>1.066887083E9</v>
-      </c>
-      <c r="F168" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B169" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="C169" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="D169" s="3">
-        <v>-6.202138299E9</v>
-      </c>
-      <c r="E169" s="3">
-        <v>1.066887083E9</v>
-      </c>
-      <c r="F169" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B170" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="C170" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="D170" s="3">
-        <v>-6.199785161E9</v>
-      </c>
-      <c r="E170" s="3">
-        <v>1.066922066E9</v>
-      </c>
-      <c r="F170" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B171" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="C171" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="D171" s="3">
-        <v>-6.199785161E9</v>
-      </c>
-      <c r="E171" s="3">
-        <v>1.066922066E9</v>
-      </c>
-      <c r="F171" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B172" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="C172" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="D172" s="3">
-        <v>-6.199785161E9</v>
-      </c>
-      <c r="E172" s="3">
-        <v>1.066922066E9</v>
-      </c>
-      <c r="F172" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B173" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="C173" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="D173" s="3">
-        <v>-6.199473566E9</v>
-      </c>
-      <c r="E173" s="3">
-        <v>1.066963347E9</v>
-      </c>
-      <c r="F173" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B174" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="C174" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="D174" s="3">
-        <v>-6.199473566E9</v>
-      </c>
-      <c r="E174" s="3">
-        <v>1.066963347E9</v>
-      </c>
-      <c r="F174" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B175" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="C175" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="D175" s="3">
-        <v>-6.199473566E9</v>
-      </c>
-      <c r="E175" s="3">
-        <v>1.066963347E9</v>
-      </c>
-      <c r="F175" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B176" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="C176" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="D176" s="3">
-        <v>-6.197312075E9</v>
-      </c>
-      <c r="E176" s="3">
-        <v>1.066992734E9</v>
-      </c>
-      <c r="F176" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B177" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="C177" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="D177" s="3">
-        <v>-6.197312075E9</v>
-      </c>
-      <c r="E177" s="3">
-        <v>1.066992734E9</v>
-      </c>
-      <c r="F177" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B178" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="C178" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="D178" s="3">
-        <v>-6.197312075E9</v>
-      </c>
-      <c r="E178" s="3">
-        <v>1.066992734E9</v>
-      </c>
-      <c r="F178" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B179" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="C179" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="D179" s="3">
-        <v>-6.195070643E9</v>
-      </c>
-      <c r="E179" s="3">
-        <v>1.067017599E9</v>
-      </c>
-      <c r="F179" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B180" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="C180" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="D180" s="3">
-        <v>-6.195070643E9</v>
-      </c>
-      <c r="E180" s="3">
-        <v>1.067017599E9</v>
-      </c>
-      <c r="F180" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B181" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="C181" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="D181" s="3">
-        <v>-6.195070643E9</v>
-      </c>
-      <c r="E181" s="3">
-        <v>1.067017599E9</v>
-      </c>
-      <c r="F181" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B182" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="C182" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="D182" s="3">
-        <v>-6.197810282E9</v>
-      </c>
-      <c r="E182" s="3">
-        <v>1.067046329E9</v>
-      </c>
-      <c r="F182" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B183" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="C183" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="D183" s="3">
-        <v>-6.197810282E9</v>
-      </c>
-      <c r="E183" s="3">
-        <v>1.067046329E9</v>
-      </c>
-      <c r="F183" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B184" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="C184" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="D184" s="3">
-        <v>-6.197810282E9</v>
-      </c>
-      <c r="E184" s="3">
-        <v>1.067046329E9</v>
-      </c>
-      <c r="F184" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B185" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="C185" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="D185" s="3">
-        <v>-6.196307179E9</v>
-      </c>
-      <c r="E185" s="3">
-        <v>1.067080886E9</v>
-      </c>
-      <c r="F185" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B186" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="C186" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="D186" s="3">
-        <v>-6.196307179E9</v>
-      </c>
-      <c r="E186" s="3">
-        <v>1.067080886E9</v>
-      </c>
-      <c r="F186" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B187" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="C187" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="D187" s="3">
-        <v>-6.196307179E9</v>
-      </c>
-      <c r="E187" s="3">
-        <v>1.067080886E9</v>
-      </c>
-      <c r="F187" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B188" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="C188" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="D188" s="3">
-        <v>-6.192330082E9</v>
-      </c>
-      <c r="E188" s="3">
-        <v>1.067104249E9</v>
-      </c>
-      <c r="F188" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B189" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="C189" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="D189" s="3">
-        <v>-6.192330082E9</v>
-      </c>
-      <c r="E189" s="3">
-        <v>1.067104249E9</v>
-      </c>
-      <c r="F189" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B190" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="C190" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="D190" s="3">
-        <v>-6.192330082E9</v>
-      </c>
-      <c r="E190" s="3">
-        <v>1.067104249E9</v>
-      </c>
-      <c r="F190" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B191" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="C191" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="D191" s="3">
-        <v>-6.18956417E8</v>
-      </c>
-      <c r="E191" s="3">
-        <v>1.067129097E9</v>
-      </c>
-      <c r="F191" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B192" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="C192" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="D192" s="3">
-        <v>-6.18956417E8</v>
-      </c>
-      <c r="E192" s="3">
-        <v>1.067129097E9</v>
-      </c>
-      <c r="F192" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B193" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="C193" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="D193" s="3">
-        <v>-6.18956417E8</v>
-      </c>
-      <c r="E193" s="3">
-        <v>1.067129097E9</v>
-      </c>
-      <c r="F193" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B194" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="C194" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="D194" s="3">
-        <v>-6.189822446E9</v>
-      </c>
-      <c r="E194" s="3">
-        <v>1.067169312E9</v>
-      </c>
-      <c r="F194" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B195" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="C195" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="D195" s="3">
-        <v>-6.189822446E9</v>
-      </c>
-      <c r="E195" s="3">
-        <v>1.067169312E9</v>
-      </c>
-      <c r="F195" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B196" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="C196" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="D196" s="3">
-        <v>-6.189822446E9</v>
-      </c>
-      <c r="E196" s="3">
-        <v>1.067169312E9</v>
-      </c>
-      <c r="F196" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B197" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="C197" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="D197" s="3">
-        <v>-6.171664475E9</v>
-      </c>
-      <c r="E197" s="3">
-        <v>1.067277327E9</v>
-      </c>
-      <c r="F197" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B198" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="C198" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="D198" s="3">
-        <v>-6.171664475E9</v>
-      </c>
-      <c r="E198" s="3">
-        <v>1.067277327E9</v>
-      </c>
-      <c r="F198" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B199" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="C199" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="D199" s="3">
-        <v>-6.171664475E9</v>
-      </c>
-      <c r="E199" s="3">
-        <v>1.067277327E9</v>
-      </c>
-      <c r="F199" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B200" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="C200" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="D200" s="3">
-        <v>-6.171664475E9</v>
-      </c>
-      <c r="E200" s="3">
-        <v>1.067277327E9</v>
-      </c>
-      <c r="F200" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B201" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="C201" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="D201" s="3">
-        <v>-6.171664475E9</v>
-      </c>
-      <c r="E201" s="3">
-        <v>1.067277327E9</v>
-      </c>
-      <c r="F201" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="202">
-      <c r="A202" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B202" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="C202" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="D202" s="3">
-        <v>-6.171664475E9</v>
-      </c>
-      <c r="E202" s="3">
-        <v>1.067277327E9</v>
-      </c>
-      <c r="F202" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B203" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="C203" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="D203" s="3">
-        <v>-6.175182254E9</v>
-      </c>
-      <c r="E203" s="3">
-        <v>1.067279483E9</v>
-      </c>
-      <c r="F203" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="204">
-      <c r="A204" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B204" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="C204" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="D204" s="3">
-        <v>-6.175182254E9</v>
-      </c>
-      <c r="E204" s="3">
-        <v>1.067279483E9</v>
-      </c>
-      <c r="F204" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B205" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="C205" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="D205" s="3">
-        <v>-6.175182254E9</v>
-      </c>
-      <c r="E205" s="3">
-        <v>1.067279483E9</v>
-      </c>
-      <c r="F205" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="206">
-      <c r="A206" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B206" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="C206" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="D206" s="3">
-        <v>-6.175182254E9</v>
-      </c>
-      <c r="E206" s="3">
-        <v>1.067279483E9</v>
-      </c>
-      <c r="F206" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="207">
-      <c r="A207" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B207" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="C207" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="D207" s="3">
-        <v>-6.175182254E9</v>
-      </c>
-      <c r="E207" s="3">
-        <v>1.067279483E9</v>
-      </c>
-      <c r="F207" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="208">
-      <c r="A208" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B208" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="C208" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="D208" s="3">
-        <v>-6.175182254E9</v>
-      </c>
-      <c r="E208" s="3">
-        <v>1.067279483E9</v>
-      </c>
-      <c r="F208" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="209">
-      <c r="A209" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B209" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="C209" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="D209" s="3">
-        <v>-6.17816597E8</v>
-      </c>
-      <c r="E209" s="3">
-        <v>1.067282659E9</v>
-      </c>
-      <c r="F209" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="210">
-      <c r="A210" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B210" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="C210" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="D210" s="3">
-        <v>-6.17816597E8</v>
-      </c>
-      <c r="E210" s="3">
-        <v>1.067282659E9</v>
-      </c>
-      <c r="F210" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="211">
-      <c r="A211" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B211" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="C211" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="D211" s="3">
-        <v>-6.17816597E8</v>
-      </c>
-      <c r="E211" s="3">
-        <v>1.067282659E9</v>
-      </c>
-      <c r="F211" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="212">
-      <c r="A212" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B212" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="C212" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="D212" s="3">
-        <v>-6.17816597E8</v>
-      </c>
-      <c r="E212" s="3">
-        <v>1.067282659E9</v>
-      </c>
-      <c r="F212" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="213">
-      <c r="A213" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B213" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="C213" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="D213" s="3">
-        <v>-6.17816597E8</v>
-      </c>
-      <c r="E213" s="3">
-        <v>1.067282659E9</v>
-      </c>
-      <c r="F213" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="214">
-      <c r="A214" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B214" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="C214" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="D214" s="3">
-        <v>-6.17816597E8</v>
-      </c>
-      <c r="E214" s="3">
-        <v>1.067282659E9</v>
-      </c>
-      <c r="F214" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="215">
-      <c r="A215" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B215" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="C215" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="D215" s="3">
-        <v>-6.181522685E9</v>
-      </c>
-      <c r="E215" s="3">
-        <v>1.06728885E8</v>
-      </c>
-      <c r="F215" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="216">
-      <c r="A216" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B216" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="C216" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="D216" s="3">
-        <v>-6.181522685E9</v>
-      </c>
-      <c r="E216" s="3">
-        <v>1.06728885E8</v>
-      </c>
-      <c r="F216" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="217">
-      <c r="A217" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B217" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="C217" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="D217" s="3">
-        <v>-6.181522685E9</v>
-      </c>
-      <c r="E217" s="3">
-        <v>1.06728885E8</v>
-      </c>
-      <c r="F217" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="218">
-      <c r="A218" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B218" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="C218" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="D218" s="3">
-        <v>-6.181522685E9</v>
-      </c>
-      <c r="E218" s="3">
-        <v>1.06728885E8</v>
-      </c>
-      <c r="F218" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="219">
-      <c r="A219" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B219" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="C219" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="D219" s="3">
-        <v>-6.181522685E9</v>
-      </c>
-      <c r="E219" s="3">
-        <v>1.06728885E8</v>
-      </c>
-      <c r="F219" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="220">
-      <c r="A220" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B220" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="C220" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="D220" s="3">
-        <v>-6.181522685E9</v>
-      </c>
-      <c r="E220" s="3">
-        <v>1.06728885E8</v>
-      </c>
-      <c r="F220" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="221">
-      <c r="A221" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B221" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="C221" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="D221" s="3">
-        <v>-6.184816972E9</v>
-      </c>
-      <c r="E221" s="3">
-        <v>1.067297078E9</v>
-      </c>
-      <c r="F221" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="222">
-      <c r="A222" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B222" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="C222" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="D222" s="3">
-        <v>-6.184816972E9</v>
-      </c>
-      <c r="E222" s="3">
-        <v>1.067297078E9</v>
-      </c>
-      <c r="F222" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="223">
-      <c r="A223" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B223" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="C223" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="D223" s="3">
-        <v>-6.184816972E9</v>
-      </c>
-      <c r="E223" s="3">
-        <v>1.067297078E9</v>
-      </c>
-      <c r="F223" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="224">
-      <c r="A224" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B224" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="C224" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="D224" s="3">
-        <v>-6.184816972E9</v>
-      </c>
-      <c r="E224" s="3">
-        <v>1.067297078E9</v>
-      </c>
-      <c r="F224" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="225">
-      <c r="A225" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B225" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="C225" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="D225" s="3">
-        <v>-6.184816972E9</v>
-      </c>
-      <c r="E225" s="3">
-        <v>1.067297078E9</v>
-      </c>
-      <c r="F225" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="226">
-      <c r="A226" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B226" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="C226" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="D226" s="3">
-        <v>-6.184816972E9</v>
-      </c>
-      <c r="E226" s="3">
-        <v>1.067297078E9</v>
-      </c>
-      <c r="F226" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="227">
-      <c r="A227" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B227" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="C227" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="D227" s="3">
-        <v>-6.185604862E9</v>
-      </c>
-      <c r="E227" s="3">
-        <v>1.067268604E9</v>
-      </c>
-      <c r="F227" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="228">
-      <c r="A228" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B228" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="C228" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="D228" s="3">
-        <v>-6.185604862E9</v>
-      </c>
-      <c r="E228" s="3">
-        <v>1.067268604E9</v>
-      </c>
-      <c r="F228" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="229">
-      <c r="A229" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B229" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="C229" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="D229" s="3">
-        <v>-6.185604862E9</v>
-      </c>
-      <c r="E229" s="3">
-        <v>1.067268604E9</v>
-      </c>
-      <c r="F229" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="230">
-      <c r="A230" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B230" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="C230" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="D230" s="3">
-        <v>-6.185604862E9</v>
-      </c>
-      <c r="E230" s="3">
-        <v>1.067268604E9</v>
-      </c>
-      <c r="F230" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="231">
-      <c r="A231" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B231" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="C231" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="D231" s="3">
-        <v>-6.185604862E9</v>
-      </c>
-      <c r="E231" s="3">
-        <v>1.067268604E9</v>
-      </c>
-      <c r="F231" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="232">
-      <c r="A232" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B232" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="C232" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="D232" s="3">
-        <v>-6.185604862E9</v>
-      </c>
-      <c r="E232" s="3">
-        <v>1.067268604E9</v>
-      </c>
-      <c r="F232" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="233">
-      <c r="A233" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B233" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="C233" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="D233" s="3">
-        <v>-6.187218306E9</v>
-      </c>
-      <c r="E233" s="3">
-        <v>1.067241545E9</v>
-      </c>
-      <c r="F233" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="234">
-      <c r="A234" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B234" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="C234" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="D234" s="3">
-        <v>-6.187218306E9</v>
-      </c>
-      <c r="E234" s="3">
-        <v>1.067241545E9</v>
-      </c>
-      <c r="F234" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="235">
-      <c r="A235" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B235" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="C235" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="D235" s="3">
-        <v>-6.187218306E9</v>
-      </c>
-      <c r="E235" s="3">
-        <v>1.067241545E9</v>
-      </c>
-      <c r="F235" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="236">
-      <c r="A236" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B236" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="C236" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="D236" s="3">
-        <v>-6.187218306E9</v>
-      </c>
-      <c r="E236" s="3">
-        <v>1.067241545E9</v>
-      </c>
-      <c r="F236" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="237">
-      <c r="A237" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B237" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="C237" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="D237" s="3">
-        <v>-6.187218306E9</v>
-      </c>
-      <c r="E237" s="3">
-        <v>1.067241545E9</v>
-      </c>
-      <c r="F237" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="238">
-      <c r="A238" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B238" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="C238" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="D238" s="3">
-        <v>-6.187218306E9</v>
-      </c>
-      <c r="E238" s="3">
-        <v>1.067241545E9</v>
-      </c>
-      <c r="F238" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="239">
-      <c r="A239" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B239" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="C239" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="D239" s="3">
-        <v>-6.188080812E9</v>
-      </c>
-      <c r="E239" s="3">
-        <v>1.067212383E9</v>
-      </c>
-      <c r="F239" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="240">
-      <c r="A240" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B240" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="C240" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="D240" s="3">
-        <v>-6.188080812E9</v>
-      </c>
-      <c r="E240" s="3">
-        <v>1.067212383E9</v>
-      </c>
-      <c r="F240" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="241">
-      <c r="A241" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B241" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="C241" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="D241" s="3">
-        <v>-6.188080812E9</v>
-      </c>
-      <c r="E241" s="3">
-        <v>1.067212383E9</v>
-      </c>
-      <c r="F241" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="242">
-      <c r="A242" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B242" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="C242" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="D242" s="3">
-        <v>-6.188080812E9</v>
-      </c>
-      <c r="E242" s="3">
-        <v>1.067212383E9</v>
-      </c>
-      <c r="F242" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="243">
-      <c r="A243" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B243" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="C243" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="D243" s="3">
-        <v>-6.188080812E9</v>
-      </c>
-      <c r="E243" s="3">
-        <v>1.067212383E9</v>
-      </c>
-      <c r="F243" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="244">
-      <c r="A244" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B244" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="C244" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="D244" s="3">
-        <v>-6.188080812E9</v>
-      </c>
-      <c r="E244" s="3">
-        <v>1.067212383E9</v>
-      </c>
-      <c r="F244" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="245">
-      <c r="A245" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B245" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="C245" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="D245" s="3">
-        <v>-6.187582823E9</v>
-      </c>
-      <c r="E245" s="3">
-        <v>1.067224502E9</v>
-      </c>
-      <c r="F245" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="246">
-      <c r="A246" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B246" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="C246" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="D246" s="3">
-        <v>-6.187582823E9</v>
-      </c>
-      <c r="E246" s="3">
-        <v>1.067224502E9</v>
-      </c>
-      <c r="F246" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="247">
-      <c r="A247" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B247" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="C247" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="D247" s="3">
-        <v>-6.187582823E9</v>
-      </c>
-      <c r="E247" s="3">
-        <v>1.067224502E9</v>
-      </c>
-      <c r="F247" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="248">
-      <c r="A248" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B248" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="C248" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="D248" s="3">
-        <v>-6.187630789E9</v>
-      </c>
-      <c r="E248" s="3">
-        <v>1.067226349E9</v>
-      </c>
-      <c r="F248" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="249">
-      <c r="A249" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B249" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="C249" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="D249" s="3">
-        <v>-6.186596818E9</v>
-      </c>
-      <c r="E249" s="3">
-        <v>1.067251902E9</v>
-      </c>
-      <c r="F249" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="250">
-      <c r="A250" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B250" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="C250" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="D250" s="3">
-        <v>-6.186596818E9</v>
-      </c>
-      <c r="E250" s="3">
-        <v>1.067251902E9</v>
-      </c>
-      <c r="F250" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="251">
-      <c r="A251" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B251" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="C251" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="D251" s="3">
-        <v>-6.186596818E9</v>
-      </c>
-      <c r="E251" s="3">
-        <v>1.067251902E9</v>
-      </c>
-      <c r="F251" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="252">
-      <c r="A252" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B252" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="C252" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="D252" s="3">
-        <v>-6.185564703E9</v>
-      </c>
-      <c r="E252" s="3">
-        <v>1.067267146E9</v>
-      </c>
-      <c r="F252" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="253">
-      <c r="A253" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B253" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="C253" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="D253" s="3">
-        <v>-6.185564703E9</v>
-      </c>
-      <c r="E253" s="3">
-        <v>1.067267146E9</v>
-      </c>
-      <c r="F253" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="254">
-      <c r="A254" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B254" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="C254" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="D254" s="3">
-        <v>-6.186615412E9</v>
-      </c>
-      <c r="E254" s="3">
-        <v>1.067253364E9</v>
-      </c>
-      <c r="F254" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="255">
-      <c r="A255" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B255" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="C255" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="D255" s="3">
-        <v>-6.185753257E9</v>
-      </c>
-      <c r="E255" s="3">
-        <v>1.067302106E9</v>
-      </c>
-      <c r="F255" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="256">
-      <c r="A256" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B256" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="C256" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="D256" s="3">
-        <v>-6.185753257E9</v>
-      </c>
-      <c r="E256" s="3">
-        <v>1.067302106E9</v>
-      </c>
-      <c r="F256" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="257">
-      <c r="A257" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B257" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="C257" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="D257" s="3">
-        <v>-6.185564703E9</v>
-      </c>
-      <c r="E257" s="3">
-        <v>1.067267146E9</v>
-      </c>
-      <c r="F257" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="258">
-      <c r="A258" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B258" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="C258" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="D258" s="3">
-        <v>-6.189565202E9</v>
-      </c>
-      <c r="E258" s="3">
-        <v>1.067298684E9</v>
-      </c>
-      <c r="F258" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="259">
-      <c r="A259" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B259" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="C259" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="D259" s="3">
-        <v>-6.189565202E9</v>
-      </c>
-      <c r="E259" s="3">
-        <v>1.067298684E9</v>
-      </c>
-      <c r="F259" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="260">
-      <c r="A260" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B260" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="C260" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="D260" s="3">
-        <v>-6.185558707E9</v>
-      </c>
-      <c r="E260" s="3">
-        <v>1.067268494E9</v>
-      </c>
-      <c r="F260" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="261">
-      <c r="A261" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B261" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="C261" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="D261" s="3">
-        <v>-6.187630789E9</v>
-      </c>
-      <c r="E261" s="3">
-        <v>1.067226349E9</v>
-      </c>
-      <c r="F261" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="262">
-      <c r="A262" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B262" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="C262" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="D262" s="3">
-        <v>-6.187630789E9</v>
-      </c>
-      <c r="E262" s="3">
-        <v>1.067226349E9</v>
-      </c>
-      <c r="F262" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="263">
-      <c r="A263" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B263" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="C263" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="D263" s="3">
-        <v>-6.185753257E9</v>
-      </c>
-      <c r="E263" s="3">
-        <v>1.067302106E9</v>
-      </c>
-      <c r="F263" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="264">
-      <c r="A264" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B264" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="C264" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="D264" s="3">
-        <v>-6.186615412E9</v>
-      </c>
-      <c r="E264" s="3">
-        <v>1.067253364E9</v>
-      </c>
-      <c r="F264" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="265">
-      <c r="A265" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B265" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="C265" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="D265" s="3">
-        <v>-6.186615412E9</v>
-      </c>
-      <c r="E265" s="3">
-        <v>1.067253364E9</v>
-      </c>
-      <c r="F265" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="266">
-      <c r="A266" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B266" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="C266" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="D266" s="3">
-        <v>-6.185765988E9</v>
-      </c>
-      <c r="E266" s="3">
-        <v>1.067301557E9</v>
-      </c>
-      <c r="F266" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="267">
-      <c r="A267" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B267" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="C267" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="D267" s="3">
-        <v>-6.185558707E9</v>
-      </c>
-      <c r="E267" s="3">
-        <v>1.067268494E9</v>
-      </c>
-      <c r="F267" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="268">
-      <c r="A268" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B268" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="C268" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="D268" s="3">
-        <v>-6.185558707E9</v>
-      </c>
-      <c r="E268" s="3">
-        <v>1.067268494E9</v>
-      </c>
-      <c r="F268" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="269">
-      <c r="A269" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B269" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="C269" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="D269" s="3">
-        <v>-6.189565202E9</v>
-      </c>
-      <c r="E269" s="3">
-        <v>1.067298684E9</v>
-      </c>
-      <c r="F269" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="270">
-      <c r="A270" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B270" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="C270" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="D270" s="3">
-        <v>-6.185765988E9</v>
-      </c>
-      <c r="E270" s="3">
-        <v>1.067301557E9</v>
-      </c>
-      <c r="F270" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="271">
-      <c r="A271" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B271" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="C271" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="D271" s="3">
-        <v>-6.185765988E9</v>
-      </c>
-      <c r="E271" s="3">
-        <v>1.067301557E9</v>
-      </c>
-      <c r="F271" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="272">
-      <c r="A272" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B272" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="C272" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="D272" s="3">
-        <v>-6.189551826E9</v>
-      </c>
-      <c r="E272" s="3">
-        <v>1.067298209E9</v>
-      </c>
-      <c r="F272" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="273">
-      <c r="A273" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B273" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="C273" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="D273" s="3">
-        <v>-6.189551826E9</v>
-      </c>
-      <c r="E273" s="3">
-        <v>1.067298209E9</v>
-      </c>
-      <c r="F273" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="274">
-      <c r="A274" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B274" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="C274" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="D274" s="3">
-        <v>-6.189551826E9</v>
-      </c>
-      <c r="E274" s="3">
-        <v>1.067298209E9</v>
-      </c>
-      <c r="F274" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="275">
-      <c r="A275" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B275" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="C275" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="D275" s="3">
-        <v>-6.196451622E9</v>
-      </c>
-      <c r="E275" s="3">
-        <v>1.067081613E9</v>
-      </c>
-      <c r="F275" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="276">
-      <c r="A276" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B276" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="C276" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="D276" s="3">
-        <v>-6.192492899E9</v>
-      </c>
-      <c r="E276" s="3">
-        <v>1.067104074E9</v>
-      </c>
-      <c r="F276" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="277">
-      <c r="A277" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B277" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="C277" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="D277" s="3">
-        <v>-6.189609031E9</v>
-      </c>
-      <c r="E277" s="3">
-        <v>1.067130183E9</v>
-      </c>
-      <c r="F277" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="278">
-      <c r="A278" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B278" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="C278" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="D278" s="3">
-        <v>-6.1898949E7</v>
-      </c>
-      <c r="E278" s="3">
-        <v>1.067168953E9</v>
-      </c>
-      <c r="F278" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="279">
-      <c r="A279" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B279" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="C279" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="D279" s="3">
-        <v>-61972.0</v>
-      </c>
-      <c r="E279" s="3">
-        <v>1067067.0</v>
-      </c>
-      <c r="F279" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="280">
-      <c r="A280" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B280" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="C280" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="D280" s="3">
-        <v>-61972.0</v>
-      </c>
-      <c r="E280" s="3">
-        <v>1067067.0</v>
-      </c>
-      <c r="F280" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="281">
-      <c r="A281" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B281" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="C281" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="D281" s="3">
-        <v>-61972.0</v>
-      </c>
-      <c r="E281" s="3">
-        <v>1067067.0</v>
-      </c>
-      <c r="F281" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="282">
-      <c r="A282" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B282" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="C282" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="D282" s="3">
-        <v>-6.196451622E9</v>
-      </c>
-      <c r="E282" s="3">
-        <v>1.067081613E9</v>
-      </c>
-      <c r="F282" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="283">
-      <c r="A283" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B283" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="C283" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="D283" s="3">
-        <v>-6.196451622E9</v>
-      </c>
-      <c r="E283" s="3">
-        <v>1.067081613E9</v>
-      </c>
-      <c r="F283" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="284">
-      <c r="A284" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B284" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="C284" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="D284" s="3">
-        <v>-6.192492899E9</v>
-      </c>
-      <c r="E284" s="3">
-        <v>1.067104074E9</v>
-      </c>
-      <c r="F284" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="285">
-      <c r="A285" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B285" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="C285" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="D285" s="3">
-        <v>-6.192492899E9</v>
-      </c>
-      <c r="E285" s="3">
-        <v>1.067104074E9</v>
-      </c>
-      <c r="F285" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="286">
-      <c r="A286" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B286" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="C286" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="D286" s="3">
-        <v>-6.189609031E9</v>
-      </c>
-      <c r="E286" s="3">
-        <v>1.067130183E9</v>
-      </c>
-      <c r="F286" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="287">
-      <c r="A287" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B287" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="C287" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="D287" s="3">
-        <v>-6.189609031E9</v>
-      </c>
-      <c r="E287" s="3">
-        <v>1.067130183E9</v>
-      </c>
-      <c r="F287" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="288">
-      <c r="A288" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B288" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="C288" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="D288" s="3">
-        <v>-6.1898949E7</v>
-      </c>
-      <c r="E288" s="3">
-        <v>1.067168953E9</v>
-      </c>
-      <c r="F288" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="289">
-      <c r="A289" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B289" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="C289" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="D289" s="3">
-        <v>-6.1898949E7</v>
-      </c>
-      <c r="E289" s="3">
-        <v>1.067168953E9</v>
-      </c>
-      <c r="F289" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="290">
-      <c r="A290" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B290" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="C290" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="D290" s="3">
-        <v>-6.245096996E9</v>
-      </c>
-      <c r="E290" s="3">
-        <v>1.06611612E8</v>
-      </c>
-      <c r="F290" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="291">
-      <c r="A291" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B291" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="C291" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="D291" s="3">
-        <v>-6.245096996E9</v>
-      </c>
-      <c r="E291" s="3">
-        <v>1.06611612E8</v>
-      </c>
-      <c r="F291" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="292">
-      <c r="A292" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B292" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="C292" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="D292" s="3">
-        <v>-6.245096996E9</v>
-      </c>
-      <c r="E292" s="3">
-        <v>1.06611612E8</v>
-      </c>
-      <c r="F292" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="293">
-      <c r="A293" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B293" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="C293" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="D293" s="3">
-        <v>-6.243126004E9</v>
-      </c>
-      <c r="E293" s="3">
-        <v>1.06616485E8</v>
-      </c>
-      <c r="F293" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="294">
-      <c r="A294" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B294" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="C294" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="D294" s="3">
-        <v>-6.243126004E9</v>
-      </c>
-      <c r="E294" s="3">
-        <v>1.06616485E8</v>
-      </c>
-      <c r="F294" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="295">
-      <c r="A295" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B295" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="C295" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="D295" s="3">
-        <v>-6.243126004E9</v>
-      </c>
-      <c r="E295" s="3">
-        <v>1.06616485E8</v>
-      </c>
-      <c r="F295" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="296">
-      <c r="A296" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B296" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="C296" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="D296" s="3">
-        <v>-6.242830004E9</v>
-      </c>
-      <c r="E296" s="3">
-        <v>1.06621432E8</v>
-      </c>
-      <c r="F296" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="297">
-      <c r="A297" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B297" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="C297" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="D297" s="3">
-        <v>-6.242830004E9</v>
-      </c>
-      <c r="E297" s="3">
-        <v>1.06621432E8</v>
-      </c>
-      <c r="F297" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="298">
-      <c r="A298" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B298" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="C298" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="D298" s="3">
-        <v>-6.242830004E9</v>
-      </c>
-      <c r="E298" s="3">
-        <v>1.06621432E8</v>
-      </c>
-      <c r="F298" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="299">
-      <c r="A299" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B299" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="C299" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="D299" s="3">
-        <v>-6.242863001E9</v>
-      </c>
-      <c r="E299" s="3">
-        <v>1.06625613E8</v>
-      </c>
-      <c r="F299" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="300">
-      <c r="A300" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B300" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="C300" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="D300" s="3">
-        <v>-6.242863001E9</v>
-      </c>
-      <c r="E300" s="3">
-        <v>1.06625613E8</v>
-      </c>
-      <c r="F300" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="301">
-      <c r="A301" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B301" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="C301" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="D301" s="3">
-        <v>-6.242863001E9</v>
-      </c>
-      <c r="E301" s="3">
-        <v>1.06625613E8</v>
-      </c>
-      <c r="F301" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="302">
-      <c r="A302" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B302" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="C302" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="D302" s="3">
-        <v>-6.243502005E9</v>
-      </c>
-      <c r="E302" s="3">
-        <v>1.06631477E8</v>
-      </c>
-      <c r="F302" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="303">
-      <c r="A303" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B303" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="C303" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="D303" s="3">
-        <v>-6.243502005E9</v>
-      </c>
-      <c r="E303" s="3">
-        <v>1.06631477E8</v>
-      </c>
-      <c r="F303" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="304">
-      <c r="A304" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B304" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="C304" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="D304" s="3">
-        <v>-6.243502005E9</v>
-      </c>
-      <c r="E304" s="3">
-        <v>1.06631477E8</v>
-      </c>
-      <c r="F304" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="305">
-      <c r="A305" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B305" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="C305" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="D305" s="3">
-        <v>-6245455.0</v>
-      </c>
-      <c r="E305" s="3">
-        <v>1.06634934E8</v>
-      </c>
-      <c r="F305" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="306">
-      <c r="A306" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B306" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="C306" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="D306" s="3">
-        <v>-6245455.0</v>
-      </c>
-      <c r="E306" s="3">
-        <v>1.06634934E8</v>
-      </c>
-      <c r="F306" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="307">
-      <c r="A307" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B307" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="C307" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="D307" s="3">
-        <v>-6245455.0</v>
-      </c>
-      <c r="E307" s="3">
-        <v>1.06634934E8</v>
-      </c>
-      <c r="F307" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="308">
-      <c r="A308" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B308" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="C308" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="D308" s="3">
-        <v>-6.243185999E9</v>
-      </c>
-      <c r="E308" s="3">
-        <v>1.06637889E8</v>
-      </c>
-      <c r="F308" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="309">
-      <c r="A309" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B309" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="C309" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="D309" s="3">
-        <v>-6.243185999E9</v>
-      </c>
-      <c r="E309" s="3">
-        <v>1.06637889E8</v>
-      </c>
-      <c r="F309" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="310">
-      <c r="A310" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B310" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="C310" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="D310" s="3">
-        <v>-6.243185999E9</v>
-      </c>
-      <c r="E310" s="3">
-        <v>1.06637889E8</v>
-      </c>
-      <c r="F310" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="311">
-      <c r="A311" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B311" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="C311" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="D311" s="3">
-        <v>-6.243172998E9</v>
-      </c>
-      <c r="E311" s="3">
-        <v>1.06640725E8</v>
-      </c>
-      <c r="F311" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="312">
-      <c r="A312" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B312" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="C312" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="D312" s="3">
-        <v>-6.243172998E9</v>
-      </c>
-      <c r="E312" s="3">
-        <v>1.06640725E8</v>
-      </c>
-      <c r="F312" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="313">
-      <c r="A313" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B313" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="C313" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="D313" s="3">
-        <v>-6.243172998E9</v>
-      </c>
-      <c r="E313" s="3">
-        <v>1.06640725E8</v>
-      </c>
-      <c r="F313" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="314">
-      <c r="A314" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B314" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="C314" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="D314" s="3">
-        <v>-6.245195004E9</v>
-      </c>
-      <c r="E314" s="3">
-        <v>1.06611803E8</v>
-      </c>
-      <c r="F314" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="315">
-      <c r="A315" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B315" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="C315" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="D315" s="3">
-        <v>-6.245195004E9</v>
-      </c>
-      <c r="E315" s="3">
-        <v>1.06611803E8</v>
-      </c>
-      <c r="F315" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="316">
-      <c r="A316" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B316" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="C316" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="D316" s="3">
-        <v>-6.245195004E9</v>
-      </c>
-      <c r="E316" s="3">
-        <v>1.06611803E8</v>
-      </c>
-      <c r="F316" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="317">
-      <c r="A317" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B317" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="C317" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="D317" s="3">
-        <v>-6243258.0</v>
-      </c>
-      <c r="E317" s="3">
-        <v>1.06616915E8</v>
-      </c>
-      <c r="F317" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="318">
-      <c r="A318" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B318" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="C318" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="D318" s="3">
-        <v>-6243258.0</v>
-      </c>
-      <c r="E318" s="3">
-        <v>1.06616915E8</v>
-      </c>
-      <c r="F318" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="319">
-      <c r="A319" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B319" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="C319" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="D319" s="3">
-        <v>-6243258.0</v>
-      </c>
-      <c r="E319" s="3">
-        <v>1.06616915E8</v>
-      </c>
-      <c r="F319" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="320">
-      <c r="A320" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B320" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="C320" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="D320" s="3">
-        <v>-6.242779998E9</v>
-      </c>
-      <c r="E320" s="3">
-        <v>1.06621805E8</v>
-      </c>
-      <c r="F320" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="321">
-      <c r="A321" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B321" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="C321" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="D321" s="3">
-        <v>-6.242779998E9</v>
-      </c>
-      <c r="E321" s="3">
-        <v>1.06621805E8</v>
-      </c>
-      <c r="F321" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="322">
-      <c r="A322" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B322" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="C322" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="D322" s="3">
-        <v>-6.242779998E9</v>
-      </c>
-      <c r="E322" s="3">
-        <v>1.06621805E8</v>
-      </c>
-      <c r="F322" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="323">
-      <c r="A323" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B323" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="C323" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="D323" s="3">
-        <v>-6.242945997E9</v>
-      </c>
-      <c r="E323" s="3">
-        <v>1.06625858E8</v>
-      </c>
-      <c r="F323" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="324">
-      <c r="A324" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B324" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="C324" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="D324" s="3">
-        <v>-6.242945997E9</v>
-      </c>
-      <c r="E324" s="3">
-        <v>1.06625858E8</v>
-      </c>
-      <c r="F324" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="325">
-      <c r="A325" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B325" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="C325" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="D325" s="3">
-        <v>-6.242945997E9</v>
-      </c>
-      <c r="E325" s="3">
-        <v>1.06625858E8</v>
-      </c>
-      <c r="F325" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="326">
-      <c r="A326" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B326" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="C326" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="D326" s="3">
-        <v>-6.243495999E9</v>
-      </c>
-      <c r="E326" s="3">
-        <v>1.06631177E8</v>
-      </c>
-      <c r="F326" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="327">
-      <c r="A327" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B327" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="C327" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="D327" s="3">
-        <v>-6.243495999E9</v>
-      </c>
-      <c r="E327" s="3">
-        <v>1.06631177E8</v>
-      </c>
-      <c r="F327" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="328">
-      <c r="A328" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B328" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="C328" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="D328" s="3">
-        <v>-6.243495999E9</v>
-      </c>
-      <c r="E328" s="3">
-        <v>1.06631177E8</v>
-      </c>
-      <c r="F328" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="329">
-      <c r="A329" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B329" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="C329" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="D329" s="3">
-        <v>-6.245406004E9</v>
-      </c>
-      <c r="E329" s="3">
-        <v>1.06634705E8</v>
-      </c>
-      <c r="F329" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="330">
-      <c r="A330" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B330" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="C330" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="D330" s="3">
-        <v>-6.245406004E9</v>
-      </c>
-      <c r="E330" s="3">
-        <v>1.06634705E8</v>
-      </c>
-      <c r="F330" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="331">
-      <c r="A331" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B331" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="C331" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="D331" s="3">
-        <v>-6.245406004E9</v>
-      </c>
-      <c r="E331" s="3">
-        <v>1.06634705E8</v>
-      </c>
-      <c r="F331" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="332">
-      <c r="A332" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B332" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="C332" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="D332" s="3">
-        <v>-6.242610997E9</v>
-      </c>
-      <c r="E332" s="3">
-        <v>1.06638267E8</v>
-      </c>
-      <c r="F332" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="333">
-      <c r="A333" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B333" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="C333" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="D333" s="3">
-        <v>-6.242610997E9</v>
-      </c>
-      <c r="E333" s="3">
-        <v>1.06638267E8</v>
-      </c>
-      <c r="F333" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="334">
-      <c r="A334" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B334" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="C334" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="D334" s="3">
-        <v>-6.242610997E9</v>
-      </c>
-      <c r="E334" s="3">
-        <v>1.06638267E8</v>
-      </c>
-      <c r="F334" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="335">
-      <c r="A335" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B335" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="C335" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="D335" s="3">
-        <v>-6.243172998E9</v>
-      </c>
-      <c r="E335" s="3">
-        <v>1.06640725E8</v>
-      </c>
-      <c r="F335" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="336">
-      <c r="A336" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B336" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="C336" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="D336" s="3">
-        <v>-6.243172998E9</v>
-      </c>
-      <c r="E336" s="3">
-        <v>1.06640725E8</v>
-      </c>
-      <c r="F336" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="337">
-      <c r="A337" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B337" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="C337" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="D337" s="3">
-        <v>-6.243172998E9</v>
-      </c>
-      <c r="E337" s="3">
-        <v>1.06640725E8</v>
-      </c>
-      <c r="F337" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
   </sheetData>
+  <autoFilter ref="$A$1:$Y$337"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
